--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1413-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1413-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{731C9072-8169-4BAE-B0A6-543F1EAAE73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F2E7CD5-9C28-40E1-8F5F-8926D9C5C263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{98582DD1-EE4B-41F5-A0F5-041F44A4025E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B9556938-45D0-41CB-B9EB-A00C8AAB55D2}"/>
   </bookViews>
   <sheets>
     <sheet name="1413-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1442,22 +1442,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B46DE5-AA09-4745-AAB2-F1B39C501CE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFAF0E8-68A3-4F49-AC76-F0C4CC283763}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="14" width="6.75" customWidth="1"/>
-    <col min="15" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="9.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="14" width="5.88671875" customWidth="1"/>
+    <col min="15" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1491,7 +1491,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1647,7 +1647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2019</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>29</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>29</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2018</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2017</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2016</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2015</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2014</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2013</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2012</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2011</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2010</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2009</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2008</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2007</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2006</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2005</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2004</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2003</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2002</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2001</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2000</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1999</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>1998</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1997</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>1996</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1995</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>1994</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1993</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>1992</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1991</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>1990</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1989</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>1987</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1985</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>1984</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37" t="s">
         <v>35</v>
       </c>
